--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/report_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/report_export_testcases.xlsx
@@ -426,7 +426,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -605,7 +605,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="L14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有报告编制导出按钮权限、审计追踪查看权限和产品 P 的数据权限
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有报告编制导出按钮权限、审计追踪菜单权限和产品 P 的数据权限
 2. 系统已存在产品 P 下报告 R1，报告名称为“阿莫西林胶囊报告V1.0”，报告 R1 包含正文和 2 个附件
 3. 已成功完成一次报告 R1 的 ZIP 导出</t>
         </is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M20" t="inlineStr" s="2">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
